--- a/ms_tables/tableS4_mantel_tests_n4_E_small_fam.xlsx
+++ b/ms_tables/tableS4_mantel_tests_n4_E_small_fam.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomas/Documents/GitHub/GvsP/ms_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986C3D00-2B33-7C44-BFEE-5A2B2F52E1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F5C393-9005-114E-93C5-A3C84FAAA102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -559,19 +559,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>970279</xdr:colOff>
+      <xdr:colOff>960118</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>12120</xdr:rowOff>
+      <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{547C39C5-0B1E-094D-A2DF-F74B24FF38DC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52B1CEA0-219C-BE4E-A367-48AC14E50C6B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -579,7 +579,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4790439" y="215320"/>
+              <a:off x="4780278" y="205160"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -645,7 +645,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -703,7 +703,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -717,13 +717,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{547C39C5-0B1E-094D-A2DF-F74B24FF38DC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52B1CEA0-219C-BE4E-A367-48AC14E50C6B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -731,7 +731,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4790439" y="215320"/>
+              <a:off x="4780278" y="205160"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -770,37 +770,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -813,19 +813,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>782321</xdr:colOff>
+      <xdr:colOff>772160</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82A290CE-9B4E-474E-85C6-9637A0967B2B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1677A2A9-5427-3845-BBA6-96064C6A210E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -833,7 +833,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2702561" y="213360"/>
+              <a:off x="2692400" y="203200"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -868,6 +868,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -899,73 +957,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82A290CE-9B4E-474E-85C6-9637A0967B2B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1677A2A9-5427-3845-BBA6-96064C6A210E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -973,7 +979,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2702561" y="213360"/>
+              <a:off x="2692400" y="203200"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1003,9 +1009,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -1014,25 +1050,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1043,19 +1061,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1003249</xdr:colOff>
+      <xdr:colOff>974945</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>12743</xdr:rowOff>
+      <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11582ED5-C7B3-8E4E-9213-C0D07EFA72E4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAB29285-628B-E84C-B605-82D7ABBB6EDD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1063,7 +1081,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3746449" y="215943"/>
+              <a:off x="3714516" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1195,13 +1213,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11582ED5-C7B3-8E4E-9213-C0D07EFA72E4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAB29285-628B-E84C-B605-82D7ABBB6EDD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1209,7 +1227,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3746449" y="215943"/>
+              <a:off x="3714516" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1291,19 +1309,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>949959</xdr:colOff>
+      <xdr:colOff>943063</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>12120</xdr:rowOff>
+      <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F25310D-D6E6-7C47-9896-558DF877E7C9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDAFF2A0-9516-8543-8FB1-D7B33661FD6F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1311,7 +1329,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8356599" y="215320"/>
+              <a:off x="8354420" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1377,7 +1395,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1435,7 +1453,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1449,13 +1467,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F25310D-D6E6-7C47-9896-558DF877E7C9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDAFF2A0-9516-8543-8FB1-D7B33661FD6F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1463,7 +1481,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8356599" y="215320"/>
+              <a:off x="8354420" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1502,37 +1520,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -1545,19 +1563,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1371601</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:colOff>1373777</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>199571</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="16" name="TextBox 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{759C931A-552A-2D4C-9D18-BC9D905AA400}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03FAD299-7FFF-9F4D-A7AD-5315DB001360}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1565,7 +1583,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6268721" y="213360"/>
+              <a:off x="6272348" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1600,6 +1618,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1631,73 +1707,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="16" name="TextBox 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{759C931A-552A-2D4C-9D18-BC9D905AA400}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03FAD299-7FFF-9F4D-A7AD-5315DB001360}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1705,7 +1729,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6268721" y="213360"/>
+              <a:off x="6272348" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1735,9 +1759,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -1746,25 +1800,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1775,19 +1811,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>982929</xdr:colOff>
+      <xdr:colOff>976033</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>12743</xdr:rowOff>
+      <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="17" name="TextBox 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A139B252-8722-3240-A7A7-D5946D6547D0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE681360-37F0-854F-B690-23C5F15C33FF}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1795,7 +1831,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7312609" y="215943"/>
+              <a:off x="7307890" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1927,13 +1963,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="17" name="TextBox 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A139B252-8722-3240-A7A7-D5946D6547D0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE681360-37F0-854F-B690-23C5F15C33FF}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1941,7 +1977,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7312609" y="215943"/>
+              <a:off x="7307890" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2023,19 +2059,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>949959</xdr:colOff>
+      <xdr:colOff>970278</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>12120</xdr:rowOff>
+      <xdr:rowOff>1961</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="662579" cy="215754"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C10BD3D8-27E9-254B-A33C-9CFCA30CF24C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CB87514-E690-DB41-8BEE-E87C2AE9740D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2043,8 +2079,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11912599" y="215320"/>
-              <a:ext cx="707834" cy="181231"/>
+              <a:off x="11937635" y="201532"/>
+              <a:ext cx="662579" cy="215754"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2109,7 +2145,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2167,7 +2203,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2181,13 +2217,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C10BD3D8-27E9-254B-A33C-9CFCA30CF24C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CB87514-E690-DB41-8BEE-E87C2AE9740D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2195,8 +2231,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11912599" y="215320"/>
-              <a:ext cx="707834" cy="181231"/>
+              <a:off x="11937635" y="201532"/>
+              <a:ext cx="662579" cy="215754"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2234,37 +2270,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -2277,19 +2313,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1351281</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:colOff>1353457</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>199571</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFAA62CB-09E2-8648-9C37-A1DA620F7448}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2B71C42-54B3-EF4C-AE8F-788E45740478}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2297,7 +2333,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9824721" y="213360"/>
+              <a:off x="9835243" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2332,6 +2368,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2363,73 +2457,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFAA62CB-09E2-8648-9C37-A1DA620F7448}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2B71C42-54B3-EF4C-AE8F-788E45740478}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2437,7 +2479,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9824721" y="213360"/>
+              <a:off x="9835243" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2467,9 +2509,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -2478,25 +2550,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2507,19 +2561,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>982929</xdr:colOff>
+      <xdr:colOff>1003248</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>12743</xdr:rowOff>
+      <xdr:rowOff>2584</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="662579" cy="215754"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{932F03C3-945A-3143-980F-C5B17FFD50A0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CCC2351-C8A1-0D4A-A0C3-F1C6EAC2ECB9}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2527,8 +2581,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10868609" y="215943"/>
-              <a:ext cx="707834" cy="181231"/>
+              <a:off x="10891105" y="202155"/>
+              <a:ext cx="662579" cy="215754"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2659,13 +2713,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{932F03C3-945A-3143-980F-C5B17FFD50A0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CCC2351-C8A1-0D4A-A0C3-F1C6EAC2ECB9}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2673,8 +2727,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10868609" y="215943"/>
-              <a:ext cx="707834" cy="181231"/>
+              <a:off x="10891105" y="202155"/>
+              <a:ext cx="662579" cy="215754"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
